--- a/Finance.xlsx
+++ b/Finance.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12520"/>
+    <workbookView windowWidth="29400" windowHeight="12620"/>
   </bookViews>
   <sheets>
     <sheet name="Contribution" sheetId="1" r:id="rId1"/>
@@ -29,9 +29,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Name</t>
     </r>
     <r>
@@ -136,6 +143,9 @@
     <t>Twelve</t>
   </si>
   <si>
+    <t>1 percant</t>
+  </si>
+  <si>
     <t>Amount</t>
   </si>
   <si>
@@ -197,10 +207,24 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -677,154 +701,166 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1369,13 +1405,13 @@
   </cols>
   <sheetData>
     <row r="3" ht="18" spans="5:8">
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="8" t="s">
         <v>2</v>
       </c>
       <c r="H3" t="s">
@@ -1383,189 +1419,179 @@
       </c>
     </row>
     <row r="4" ht="17.6" spans="5:7">
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4">
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="5" ht="17.6" spans="5:7">
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4">
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8">
         <f>2000*G4</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="17.6" spans="5:8">
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="8">
         <v>10000</v>
       </c>
-      <c r="G6" s="4">
-        <f>G5</f>
-        <v>0</v>
+      <c r="G6" s="8">
+        <v>2000</v>
       </c>
       <c r="H6">
-        <f>F6+G6</f>
+        <f t="shared" ref="H6:H15" si="0">F6+G6</f>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="7" ht="17.6" spans="5:8">
+      <c r="E7" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="8">
         <v>10000</v>
       </c>
-    </row>
-    <row r="7" ht="17.6" spans="5:8">
-      <c r="E7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" s="4">
+      <c r="G7" s="8">
+        <v>2000</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="8" ht="17.6" spans="5:8">
+      <c r="E8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="8">
         <v>10000</v>
       </c>
-      <c r="G7" s="4">
-        <f>G5</f>
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <f>F7+G7</f>
+      <c r="G8" s="8">
+        <v>2000</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="9" ht="18" spans="5:8">
+      <c r="E9" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="8">
         <v>10000</v>
       </c>
-    </row>
-    <row r="8" ht="17.6" spans="5:8">
-      <c r="E8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="4">
+      <c r="G9" s="8">
+        <v>2000</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="10" ht="17.6" spans="5:8">
+      <c r="E10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="8">
         <v>10000</v>
       </c>
-      <c r="G8" s="4">
-        <f>G5</f>
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <f>F8+G8</f>
+      <c r="G10" s="8">
+        <v>2000</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="11" ht="17.6" spans="5:8">
+      <c r="E11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="8">
         <v>10000</v>
       </c>
-    </row>
-    <row r="9" ht="18" spans="5:8">
-      <c r="E9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="4">
+      <c r="G11" s="8">
+        <v>2000</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="12" ht="17.6" spans="5:8">
+      <c r="E12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="8">
         <v>10000</v>
       </c>
-      <c r="G9" s="4">
-        <f>G5</f>
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <f>F9+G9</f>
+      <c r="G12" s="8">
+        <v>2000</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="13" ht="17.6" spans="5:8">
+      <c r="E13" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="8">
         <v>10000</v>
       </c>
-    </row>
-    <row r="10" ht="17.6" spans="5:8">
-      <c r="E10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="4">
+      <c r="G13" s="8">
+        <v>2000</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="14" ht="17.6" spans="5:8">
+      <c r="E14" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="8">
         <v>10000</v>
       </c>
-      <c r="G10" s="4">
-        <f>G5</f>
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <f>F10+G10</f>
+      <c r="G14" s="8">
+        <v>2000</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="15" ht="17.6" spans="5:8">
+      <c r="E15" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="8">
         <v>10000</v>
       </c>
-    </row>
-    <row r="11" ht="17.6" spans="5:8">
-      <c r="E11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="4">
-        <v>10000</v>
-      </c>
-      <c r="G11" s="4">
-        <f>G5</f>
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <f>F11+G11</f>
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="12" ht="17.6" spans="5:8">
-      <c r="E12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="4">
-        <v>10000</v>
-      </c>
-      <c r="G12" s="4">
-        <f>G5</f>
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <f>F12+G12</f>
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="13" ht="17.6" spans="5:8">
-      <c r="E13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="4">
-        <v>10000</v>
-      </c>
-      <c r="G13" s="4">
-        <f>G5</f>
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <f>F13+G13</f>
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="14" ht="17.6" spans="5:8">
-      <c r="E14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="4">
-        <v>10000</v>
-      </c>
-      <c r="G14" s="4">
-        <f>G5</f>
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <f>F14+G14</f>
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="15" ht="17.6" spans="5:8">
-      <c r="E15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="4">
-        <v>10000</v>
-      </c>
-      <c r="G15" s="4">
-        <f>G5</f>
-        <v>0</v>
+      <c r="G15" s="8">
+        <v>2000</v>
       </c>
       <c r="H15">
-        <f>F15+G15</f>
-        <v>10000</v>
+        <f t="shared" si="0"/>
+        <v>12000</v>
       </c>
     </row>
     <row r="16" ht="17.6" spans="5:7">
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
     </row>
     <row r="17" ht="17.6" spans="5:7">
-      <c r="E17" s="3"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1576,7 +1602,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C7:AB10"/>
+  <dimension ref="A7:AB11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="4.6875" customWidth="1"/>
@@ -1641,7 +1667,10 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" ht="17" spans="3:28">
+    <row r="9" ht="17" spans="1:28">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
       <c r="C9" s="1"/>
       <c r="D9" t="e">
         <f>($F9/2)*(($E9*1%)+(($E9*1%)/$F9))</f>
@@ -1657,87 +1686,87 @@
         <f>E9/F9</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H9" s="2" t="e">
+      <c r="H9" s="5" t="e">
         <f>$G9+(($E9-(COLUMNS($H9:H9)-1)*$G9)*1%)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I9" s="2" t="e">
+      <c r="I9" s="5" t="e">
         <f>$G9+(($E9-(COLUMNS($H9:I9)-1)*$G9)*1%)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J9" s="2" t="e">
+      <c r="J9" s="5" t="e">
         <f>$G9+(($E9-(COLUMNS($H9:J9)-1)*$G9)*1%)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K9" s="2" t="e">
+      <c r="K9" s="5" t="e">
         <f>$G9+(($E9-(COLUMNS($H9:K9)-1)*$G9)*1%)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L9" s="2" t="e">
+      <c r="L9" s="5" t="e">
         <f>$G9+(($E9-(COLUMNS($H9:L9)-1)*$G9)*1%)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M9" s="2" t="e">
+      <c r="M9" s="5" t="e">
         <f>$G9+(($E9-(COLUMNS($H9:M9)-1)*$G9)*1%)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N9" s="2" t="e">
+      <c r="N9" s="5" t="e">
         <f>$G9+(($E9-(COLUMNS($H9:N9)-1)*$G9)*1%)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O9" s="2" t="e">
+      <c r="O9" s="5" t="e">
         <f>$G9+(($E9-(COLUMNS($H9:O9)-1)*$G9)*1%)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P9" s="2" t="e">
+      <c r="P9" s="5" t="e">
         <f>$G9+(($E9-(COLUMNS($H9:P9)-1)*$G9)*1%)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q9" s="2" t="e">
+      <c r="Q9" s="5" t="e">
         <f>$G9+(($E9-(COLUMNS($H9:Q9)-1)*$G9)*1%)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R9" s="2" t="str">
+      <c r="R9" s="5" t="str">
         <f>IF((COLUMN()-COLUMN($H$9)+1)&lt;=$F9,$G9+($E9*1%)*(1-((COLUMN()-COLUMN($H$9)+1)/$F9)),"")</f>
         <v/>
       </c>
-      <c r="S9" s="2" t="str">
+      <c r="S9" s="5" t="str">
         <f>IF((COLUMN()-COLUMN($H$9)+1)&lt;=$F9,$G9+($E9*1%)*(1-((COLUMN()-COLUMN($H$9)+1)/$F9)),"")</f>
         <v/>
       </c>
-      <c r="T9" s="2" t="str">
+      <c r="T9" s="5" t="str">
         <f t="shared" ref="T9:AB9" si="0">IF((COLUMN()-8)&lt;=$F9,$G9+MAX(0,($E9*1%)*(1-((COLUMN()-8)/$F9))),"")</f>
         <v/>
       </c>
-      <c r="U9" s="2" t="str">
+      <c r="U9" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="V9" s="2" t="str">
+      <c r="V9" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="W9" s="2" t="str">
+      <c r="W9" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="X9" s="2" t="str">
+      <c r="X9" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="Y9" s="2" t="str">
+      <c r="Y9" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="Z9" s="2" t="str">
+      <c r="Z9" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AA9" s="2" t="str">
+      <c r="AA9" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB9" s="2" t="str">
+      <c r="AB9" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1745,6 +1774,65 @@
     <row r="10" spans="4:5">
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11">
+        <v>0.75</v>
+      </c>
+      <c r="D11" t="e">
+        <f>($F11/2)*(($E11*0.75%)+(($E11*0.75%)/$F11))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11" t="e">
+        <f>E11/F11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H11" t="e">
+        <f>$G11+(($E11-(COLUMNS($H11:H11)-1)*$G11)*0.75%)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I11" t="e">
+        <f>$G11+(($E11-(COLUMNS($H11:I11)-1)*$G11)*0.75%)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J11" t="e">
+        <f>$G11+(($E11-(COLUMNS($H11:J11)-1)*$G11)*0.75%)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K11" t="e">
+        <f>$G11+(($E11-(COLUMNS($H11:K11)-1)*$G11)*0.75%)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L11" t="e">
+        <f>$G11+(($E11-(COLUMNS($H11:L11)-1)*$G11)*0.75%)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M11" t="e">
+        <f>$G11+(($E11-(COLUMNS($H11:M11)-1)*$G11)*0.75%)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N11" t="e">
+        <f>$G11+(($E11-(COLUMNS($H11:N11)-1)*$G11)*0.75%)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O11" t="e">
+        <f>$G11+(($E11-(COLUMNS($H11:O11)-1)*$G11)*0.75%)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P11" t="e">
+        <f>$G11+(($E11-(COLUMNS($H11:P11)-1)*$G11)*0.75%)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q11" t="e">
+        <f>$G11+(($E11-(COLUMNS($H11:Q11)-1)*$G11)*0.75%)</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1770,52 +1858,52 @@
         <v>Interest = 4250</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="U6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="4:18">
@@ -1836,50 +1924,50 @@
         <f>F7/G7</f>
         <v>5000</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="5">
         <f>H7+(F7*1%)</f>
         <v>5500</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="5">
         <f ca="1">IF((COLUMN()-8)&lt;=$F7,$G7+($E7*1%)*(1-((COLUMN()-8)/$F7)),"")</f>
         <v>5450</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="5">
         <f ca="1">IF((COLUMN()-8)&lt;=$F7,$G7+($E7*1%)*(1-((COLUMN()-8)/$F7)),"")</f>
         <v>5400</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="5">
         <f ca="1">IF((COLUMN()-8)&lt;=$F7,$G7+($E7*1%)*(1-((COLUMN()-8)/$F7)),"")</f>
         <v>5350</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7" s="5">
         <f ca="1">IF((COLUMN()-8)&lt;=$F7,$G7+($E7*1%)*(1-((COLUMN()-8)/$F7)),"")</f>
         <v>5300</v>
       </c>
-      <c r="N7" s="2">
+      <c r="N7" s="5">
         <f ca="1">IF((COLUMN()-8)&lt;=$F7,$G7+($E7*1%)*(1-((COLUMN()-8)/$F7)),"")</f>
         <v>5250</v>
       </c>
-      <c r="O7" s="2">
+      <c r="O7" s="5">
         <f ca="1">IF((COLUMN()-8)&lt;=$F7,$G7+($E7*1%)*(1-((COLUMN()-8)/$F7)),"")</f>
         <v>5200</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="5">
         <f ca="1">IF((COLUMN()-8)&lt;=$F7,$G7+($E7*1%)*(1-((COLUMN()-8)/$F7)),"")</f>
         <v>5150</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="5">
         <f ca="1">IF((COLUMN()-8)&lt;=$F7,$G7+($E7*1%)*(1-((COLUMN()-8)/$F7)),"")</f>
         <v>5100</v>
       </c>
-      <c r="R7" s="2">
+      <c r="R7" s="5">
         <f ca="1">IF((COLUMN()-8)&lt;=$F7,$G7+($E7*1%)*(1-((COLUMN()-8)/$F7)),"")</f>
         <v>5050</v>
       </c>
     </row>
     <row r="8" spans="4:13">
       <c r="D8" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E8">
         <f ca="1">($F8/2)*(($E8*1%)+(($E8*1%)/$F8))</f>
@@ -1895,38 +1983,54 @@
         <f>F8/G8</f>
         <v>10000</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="5">
         <f>H8+(F8*1%)</f>
         <v>10500</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="5">
         <f ca="1">IF((COLUMN()-8)&lt;=$F8,$G8+($E8*1%)*(1-((COLUMN()-8)/$F8)),"")</f>
         <v>10400</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8" s="5">
         <f ca="1">IF((COLUMN()-8)&lt;=$F8,$G8+($E8*1%)*(1-((COLUMN()-8)/$F8)),"")</f>
         <v>10300</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="5">
         <f ca="1">IF((COLUMN()-8)&lt;=$F8,$G8+($E8*1%)*(1-((COLUMN()-8)/$F8)),"")</f>
         <v>10200</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M8" s="5">
         <f ca="1">IF((COLUMN()-8)&lt;=$F8,$G8+($E8*1%)*(1-((COLUMN()-8)/$F8)),"")</f>
         <v>10100</v>
       </c>
     </row>
     <row r="9" spans="4:13">
-      <c r="D9" s="1"/>
-      <c r="E9"/>
-      <c r="F9" s="1"/>
-      <c r="G9"/>
-      <c r="H9"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
+      <c r="D9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="3">
+        <v>536.25</v>
+      </c>
+      <c r="F9" s="4">
+        <v>35750</v>
+      </c>
+      <c r="G9" s="3">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3">
+        <v>11917</v>
+      </c>
+      <c r="I9" s="6">
+        <v>12185</v>
+      </c>
+      <c r="J9" s="6">
+        <v>12096</v>
+      </c>
+      <c r="K9" s="6">
+        <v>12006</v>
+      </c>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Finance.xlsx
+++ b/Finance.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12620"/>
+    <workbookView windowWidth="29400" windowHeight="12620" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Contribution" sheetId="1" r:id="rId1"/>
@@ -847,10 +847,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1686,87 +1686,87 @@
         <f>E9/F9</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H9" s="5" t="e">
+      <c r="H9" s="6" t="e">
         <f>$G9+(($E9-(COLUMNS($H9:H9)-1)*$G9)*1%)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I9" s="5" t="e">
+      <c r="I9" s="6" t="e">
         <f>$G9+(($E9-(COLUMNS($H9:I9)-1)*$G9)*1%)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J9" s="5" t="e">
+      <c r="J9" s="6" t="e">
         <f>$G9+(($E9-(COLUMNS($H9:J9)-1)*$G9)*1%)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K9" s="5" t="e">
+      <c r="K9" s="6" t="e">
         <f>$G9+(($E9-(COLUMNS($H9:K9)-1)*$G9)*1%)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L9" s="5" t="e">
+      <c r="L9" s="6" t="e">
         <f>$G9+(($E9-(COLUMNS($H9:L9)-1)*$G9)*1%)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M9" s="5" t="e">
+      <c r="M9" s="6" t="e">
         <f>$G9+(($E9-(COLUMNS($H9:M9)-1)*$G9)*1%)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N9" s="5" t="e">
+      <c r="N9" s="6" t="e">
         <f>$G9+(($E9-(COLUMNS($H9:N9)-1)*$G9)*1%)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O9" s="5" t="e">
+      <c r="O9" s="6" t="e">
         <f>$G9+(($E9-(COLUMNS($H9:O9)-1)*$G9)*1%)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P9" s="5" t="e">
+      <c r="P9" s="6" t="e">
         <f>$G9+(($E9-(COLUMNS($H9:P9)-1)*$G9)*1%)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q9" s="5" t="e">
+      <c r="Q9" s="6" t="e">
         <f>$G9+(($E9-(COLUMNS($H9:Q9)-1)*$G9)*1%)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R9" s="5" t="str">
+      <c r="R9" s="6" t="str">
         <f>IF((COLUMN()-COLUMN($H$9)+1)&lt;=$F9,$G9+($E9*1%)*(1-((COLUMN()-COLUMN($H$9)+1)/$F9)),"")</f>
         <v/>
       </c>
-      <c r="S9" s="5" t="str">
+      <c r="S9" s="6" t="str">
         <f>IF((COLUMN()-COLUMN($H$9)+1)&lt;=$F9,$G9+($E9*1%)*(1-((COLUMN()-COLUMN($H$9)+1)/$F9)),"")</f>
         <v/>
       </c>
-      <c r="T9" s="5" t="str">
+      <c r="T9" s="6" t="str">
         <f t="shared" ref="T9:AB9" si="0">IF((COLUMN()-8)&lt;=$F9,$G9+MAX(0,($E9*1%)*(1-((COLUMN()-8)/$F9))),"")</f>
         <v/>
       </c>
-      <c r="U9" s="5" t="str">
+      <c r="U9" s="6" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="V9" s="5" t="str">
+      <c r="V9" s="6" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="W9" s="5" t="str">
+      <c r="W9" s="6" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="X9" s="5" t="str">
+      <c r="X9" s="6" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="Y9" s="5" t="str">
+      <c r="Y9" s="6" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="Z9" s="5" t="str">
+      <c r="Z9" s="6" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AA9" s="5" t="str">
+      <c r="AA9" s="6" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB9" s="5" t="str">
+      <c r="AB9" s="6" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1925,44 +1925,34 @@
         <v>5000</v>
       </c>
       <c r="I7" s="5">
-        <f>H7+(F7*1%)</f>
-        <v>5500</v>
+        <v>5375</v>
       </c>
       <c r="J7" s="5">
-        <f ca="1">IF((COLUMN()-8)&lt;=$F7,$G7+($E7*1%)*(1-((COLUMN()-8)/$F7)),"")</f>
-        <v>5450</v>
+        <v>5337.5</v>
       </c>
       <c r="K7" s="5">
-        <f ca="1">IF((COLUMN()-8)&lt;=$F7,$G7+($E7*1%)*(1-((COLUMN()-8)/$F7)),"")</f>
-        <v>5400</v>
+        <v>5300</v>
       </c>
       <c r="L7" s="5">
-        <f ca="1">IF((COLUMN()-8)&lt;=$F7,$G7+($E7*1%)*(1-((COLUMN()-8)/$F7)),"")</f>
-        <v>5350</v>
+        <v>5262.5</v>
       </c>
       <c r="M7" s="5">
-        <f ca="1">IF((COLUMN()-8)&lt;=$F7,$G7+($E7*1%)*(1-((COLUMN()-8)/$F7)),"")</f>
-        <v>5300</v>
+        <v>5225</v>
       </c>
       <c r="N7" s="5">
-        <f ca="1">IF((COLUMN()-8)&lt;=$F7,$G7+($E7*1%)*(1-((COLUMN()-8)/$F7)),"")</f>
-        <v>5250</v>
+        <v>5187.5</v>
       </c>
       <c r="O7" s="5">
-        <f ca="1">IF((COLUMN()-8)&lt;=$F7,$G7+($E7*1%)*(1-((COLUMN()-8)/$F7)),"")</f>
-        <v>5200</v>
+        <v>5150</v>
       </c>
       <c r="P7" s="5">
-        <f ca="1">IF((COLUMN()-8)&lt;=$F7,$G7+($E7*1%)*(1-((COLUMN()-8)/$F7)),"")</f>
-        <v>5150</v>
+        <v>5112.5</v>
       </c>
       <c r="Q7" s="5">
-        <f ca="1">IF((COLUMN()-8)&lt;=$F7,$G7+($E7*1%)*(1-((COLUMN()-8)/$F7)),"")</f>
-        <v>5100</v>
+        <v>5075</v>
       </c>
       <c r="R7" s="5">
-        <f ca="1">IF((COLUMN()-8)&lt;=$F7,$G7+($E7*1%)*(1-((COLUMN()-8)/$F7)),"")</f>
-        <v>5050</v>
+        <v>5037.5</v>
       </c>
     </row>
     <row r="8" spans="4:13">
@@ -1984,24 +1974,19 @@
         <v>10000</v>
       </c>
       <c r="I8" s="5">
-        <f>H8+(F8*1%)</f>
-        <v>10500</v>
+        <v>10375</v>
       </c>
       <c r="J8" s="5">
-        <f ca="1">IF((COLUMN()-8)&lt;=$F8,$G8+($E8*1%)*(1-((COLUMN()-8)/$F8)),"")</f>
-        <v>10400</v>
+        <v>10300</v>
       </c>
       <c r="K8" s="5">
-        <f ca="1">IF((COLUMN()-8)&lt;=$F8,$G8+($E8*1%)*(1-((COLUMN()-8)/$F8)),"")</f>
-        <v>10300</v>
+        <v>10225</v>
       </c>
       <c r="L8" s="5">
-        <f ca="1">IF((COLUMN()-8)&lt;=$F8,$G8+($E8*1%)*(1-((COLUMN()-8)/$F8)),"")</f>
-        <v>10200</v>
+        <v>10150</v>
       </c>
       <c r="M8" s="5">
-        <f ca="1">IF((COLUMN()-8)&lt;=$F8,$G8+($E8*1%)*(1-((COLUMN()-8)/$F8)),"")</f>
-        <v>10100</v>
+        <v>10075</v>
       </c>
     </row>
     <row r="9" spans="4:13">
@@ -2020,17 +2005,17 @@
       <c r="H9" s="3">
         <v>11917</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="5">
         <v>12185</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="5">
         <v>12096</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="5">
         <v>12006</v>
       </c>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
